--- a/RESULTS/tables/excluded_residents_baseline_summary.xlsx
+++ b/RESULTS/tables/excluded_residents_baseline_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>P value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Missing/Notes</t>
         </is>
       </c>
@@ -467,6 +472,7 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,6 +492,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=0</t>
         </is>
       </c>
@@ -508,6 +519,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=0</t>
         </is>
       </c>
@@ -530,6 +546,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=0</t>
         </is>
       </c>
@@ -552,6 +573,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=6861</t>
         </is>
       </c>
@@ -574,6 +600,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=6715</t>
         </is>
       </c>
@@ -596,6 +627,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=9584</t>
         </is>
       </c>
@@ -618,6 +654,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=0</t>
         </is>
       </c>
@@ -640,6 +681,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=7949</t>
         </is>
       </c>
@@ -662,6 +708,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=7949</t>
         </is>
       </c>
@@ -684,6 +735,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=19756</t>
         </is>
       </c>
@@ -706,6 +762,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=640</t>
         </is>
       </c>
@@ -728,6 +789,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Included missing=0; excluded missing=640</t>
         </is>
       </c>
@@ -749,6 +815,11 @@
         </is>
       </c>
       <c r="D15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Included missing=0; excluded missing=640</t>
         </is>

--- a/RESULTS/tables/excluded_residents_baseline_summary.xlsx
+++ b/RESULTS/tables/excluded_residents_baseline_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Characteristic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Included residents</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Excluded residents summary</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Missing/Notes</t>
         </is>
